--- a/Motoristas_Cidades.xlsx
+++ b/Motoristas_Cidades.xlsx
@@ -34,7 +34,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,20 +43,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000070C0"/>
-        <bgColor rgb="000070C0"/>
+        <fgColor rgb="000284C7"/>
+        <bgColor rgb="000284C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00004D40"/>
-        <bgColor rgb="00004D40"/>
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D3B66"/>
-        <bgColor rgb="000D3B66"/>
+        <fgColor rgb="000F766E"/>
+        <bgColor rgb="000F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,15 +78,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,16 +455,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:E210"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CIDADE</t>
@@ -478,6 +486,3394 @@
           <t>FAIXA DE CEP (OPCIONAL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BAIRROS (OPCIONAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aguas de Santa Barbara</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRUNOCORTEAVA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Apiai</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OdairA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arandu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DayaneLuise</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AntonioDonizeteAVA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CARLOSMEDEIROSAVA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EvandroAntonio</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FlavioHnerique</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GIULLIANOTAVA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JoãoVitorAVA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KAUEBASQUEAVA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KhylberdAlerrandro</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MoisesOliveira</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PauloRobertoAVA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WellingtonMaxwell</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Barao de Antonina</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AdrianoFancisco</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Barra do Chapeu</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>OdairA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Barra do Chapeu</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OdairAparecido</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Bom Sucesso de Itarare</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ArianneTereza</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bom Sucesso de Itarare</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JoseRicardoGomes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cerqueira Cesar</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TamaraEmidioAVA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Coronel Macedo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wellingtonTaquarituba</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fartura</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LucasFernando</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Iaras</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AdrieleCamile</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Iaras</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BRUNOCORTEAVA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Iaras</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vanderlucio</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Iporanga</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BrunaCollione</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Itabera</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LEONARDO-ITABERA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Itai</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Claudia2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Itai</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KhylberdAlerrandro</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Itaoca</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PauloITAOCA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AbelITAPEVA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BiancaITAPEVA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DanielITAPEVA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Davi-ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ElisarioITAPEVA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FabricioITAPEVA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HudsonITAPEVA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LucianoITAPEVA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MarizaITAPEVA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Michele2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MicheleCONTROLE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PedroITAPEVA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RafaelITAPEVA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>diegoITAPEVA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Itapirapua</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>JoseRicardoGomes</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Itapirapua Paulista</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>JhonLennon</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Itaporanga</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CesarITAPORANGA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GabrielMota</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MarcosSuntak</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Manduri</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FernandaUmbelina</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Nova Campina</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MaraCorreia</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Oleo</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>VivianeSchmidtOLEO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AdrieleCamile</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FlavioHenrique</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FlavioHnerique</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>JoãoRolimAjU</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KhylberdAlerrandro</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mauro2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ribeira</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>JhonLennon</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ribeira</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JoseRicardoGomes</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ribeirao Branco</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>JoãoVitorR2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Riversul</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AdrianoFancisco</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sarutaia</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mauro2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Taguai</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LucasFernando</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Taquarituba</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ANTONIOTAQUARITUBAAVA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Taquarituba</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>wellingtonTaquarituba</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Taquarivai</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MicheleCONTROLE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tejupa</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LucasFernando</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Timburi</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mauro2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Apiai</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Raphaela APIAI</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Arandu</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Dayane Louise</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Antonio Donizete</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CARLOS ANTONIO ROSA MEDEIROS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Evandro Antonio</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Flavio Henrique</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Giulliano Thiago</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>KAUE WILTON MORELI BASQUE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KhylberdAlerrandro</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Moises 2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Paulo Roberto</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Wellington Maxwell</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Barao de Antonina</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Adriano Francisco</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Barao de Antonina</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Adriano Riv. Bar. Cor</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Bernardino de Campos</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mateus Bernardino</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Bom Sucesso de Itarare</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ariane BOM SUCESSO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cerqueira Cesar</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tamara Emidio</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Coronel Macedo</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Adriano Francisco</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Coronel Macedo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Adriano Riv. Bar. Cor</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Fartura</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Lucas Fernando</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Holambra</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>João Rolim</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Iaras</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Bruno Aguas e iaras</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Iaras</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Vanderlucio Iaras</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Itabera</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Leo ITABERA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Itabera</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Leonardo ITABERA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Itai</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Claudia Lopes</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Itai</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EdilsonITAI</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Itai</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Khylberd Alerrandro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Abel - ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Abel ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ariane Bom sucesso</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Bianca Amaro Itapeva</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Bianca ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Claudia ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Claudia Maki ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Daniel ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Davi ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Davi Wallace Itapeva</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Diego ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Elisario ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Everton ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EvertonITAPEVA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Fabricio ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Hudson Aparecido Itapeva</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Hudson ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Luciano ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Luciano da Silva Itapeva</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Mariza ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Mariza de Almeida Itapeva</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Michele ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pedro Henrique Itapeva</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Pedro ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Rafael ITAPEVA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Rafael Jose Itapeva</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Itapirapua</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Jose Ricardo bom sucesso</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Itaporanga</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cesar ITAPORANGA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Itaporanga</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>cesar augusto itaporanga</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Edson ITARARÉ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Edson Jamil ITARARÉ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Everton ITARARÉ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gabriel Antunes</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Gabriel Antunes Itararé</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Gabriel ITARARÉ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Kelli Cristina Itararé</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Marcos ITARARE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Manduri</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Fernanda Manduri</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Nova Campina</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Mara Correia - Nova campina</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Nova Campina</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Mara Nova Campina</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Oleo</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Viviane Oleo</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Adriele Camile</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Flavio Henrique</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>João Rolim</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Khylberd Alerrandro</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Emerson Henrique Piraju</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Guilherme Piraju</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Gustavo Piraju</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Herivelton PIRAJU</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Mauro Piraju</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Sandra Piraju</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Ribeira</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Joao vitor RIBEIRÃO BRANCO</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ribeira</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Jose Ricardo bom sucesso</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Ribeirao Branco</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Joao Ribeirão B</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Ribeirao Branco</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>João Vitor RIBEIRÃO BRANCO</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Riversul</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Adriano Francisco</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Riversul</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Adriano Riv. Bar. Cor</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Sarutaia</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Juliano Aparecido TIMB-SARUT</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Taguai</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Lucas Fernando</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Taquarituba</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ANTONIO MARCOS Taquarituba</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Taquarituba</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TATIELE APARECIDA Taquarituba</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Taquarituba</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Wellington Michel Taquarituba</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Taquarivai</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Michelle TAQUARIVAI</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Tejupa</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Lucas Fernando</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Timburi</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Juliano Aparecido TIMB-SARUT</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>itararé</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Gabriel Antunes</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Loggi</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Fartura</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Loggi</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Adriano</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Akilas Vinicius</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Bruna Collione</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Daniel Carneiro</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Ederson Aparecido</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Elisario de Oliveira</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>FABIO GABRIEL DIAS RODRIGUES DA SILVA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Fabricio Leonardo</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Flavio santos Itar</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Gustavo Alves AGUAS</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Jamilly Luciano Itar</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>JessicaFerreira</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>MatheusDota</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Mauricio Rodrigues</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Michele</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Rodrigo Garcia</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>RuanHenrique</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>sem motorista</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Wellington Augusto</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Wellington Região</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Willian Ribeiro</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Imile</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>AkilasVinicius</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ArianneTerezaAVA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>B176</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>B93</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ClaudiaMaqui</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>dgomezSPD176</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>EduardoAVA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>EmersonHenrique</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>FERNANDAGOMEZAVA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>FERNANDOGOMEZ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>GustavoAlvesA</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>JulianoAparecido</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Operação01</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Operação03</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Operção02</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PauloRoberto2</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>RaquelMonitoramento</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>RuanHenrique</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>TalianeAparecida</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>TOM2</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Avaré</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -490,28 +3886,2969 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:C174"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>NOME EXATO NO SISTEMA</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>PLATAFORMA</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>STATUS NO SISTEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Abel - ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Abel ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adriano</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adriano Francisco</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Adriano Riv. Bar. Cor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Adriele Camile</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Akilas Vinicius</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Antonio Donizete</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ANTONIO MARCOS Taquarituba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ariane BOM SUCESSO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ariane Bom sucesso</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bianca Amaro Itapeva</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bianca ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bruna Collione</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bruno Aguas e iaras</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CARLOS ANTONIO ROSA MEDEIROS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cesar augusto itaporanga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cesar ITAPORANGA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Claudia ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Claudia Lopes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Claudia Maki ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Daniel Carneiro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Daniel ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Davi ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Davi Wallace Itapeva</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dayane Louise</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Diego ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DIEGO ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ederson Aparecido</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EdilsonITAI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Edson ITARARÉ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Edson Jamil ITARARÉ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Elisario de Oliveira</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Elisario ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Emerson Henrique Piraju</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Evandro Antonio</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Everton ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Everton ITARARÉ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EvertonITAPEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FABIO GABRIEL DIAS RODRIGUES DA SILVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Fabricio ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Fabricio Leonardo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Fernanda Manduri</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Flavio Henrique</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Flavio santos Itar</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gabriel Antunes Itararé</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gabriel ITARARÉ</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Giulliano Thiago</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guilherme Piraju</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gustavo Alves AGUAS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gustavo Piraju</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Herivelton PIRAJU</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hudson Aparecido Itapeva</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hudson ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jamilly Luciano Itar</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>JessicaFerreira</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Joao Ribeirão B</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jose Ricardo bom sucesso</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>João Rolim</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>João Vitor RIBEIRÃO BRANCO</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Juliano Aparecido TIMB-SARUT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>KAUE WILTON MORELI BASQUE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Kelli Cristina Itararé</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Khylberd Alerrandro</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Leo ITABERA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Leonardo ITABERA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Lucas Fernando</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Luciano da Silva Itapeva</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Luciano ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Mara Correia - Nova campina</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Mara Nova Campina</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Marcos ITARARE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Mariza de Almeida Itapeva</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Mariza ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Mateus Bernardino</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MatheusDota</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Mauricio Rodrigues</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Mauro Piraju</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Michele</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Michele ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Michelle TAQUARIVAI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Moises 2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Paulo Roberto</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Pedro Henrique Itapeva</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Pedro ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Rafael ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Rafael Jose Itapeva</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Raphaela APIAI</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Rodrigo Garcia</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>RuanHenrique</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sandra Piraju</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>sem motorista</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Tamara Emidio</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TATIELE APARECIDA Taquarituba</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Vanderlucio Iaras</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Viviane Oleo</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Wellington Augusto</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Wellington Maxwell</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Wellington Michel Taquarituba</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Wellington Região</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Willian Ribeiro</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AbelITAPEVA</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AdrianoFancisco</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AdrieleCamile</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AkilasVinicius</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AntonioDonizeteAVA</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ANTONIOTAQUARITUBAAVA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ArianneTereza</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ArianneTerezaAVA</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>B176</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>B93</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>BiancaITAPEVA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BRUNOCORTEAVA</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CARLOSMEDEIROSAVA</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CesarITAPORANGA</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Claudia2</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ClaudiaMaqui</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DanielITAPEVA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Davi-ITAPEVA</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DayaneLuise</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>dgomezSPD176</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>diegoITAPEVA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>EduardoAVA</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ElisarioITAPEVA</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>EmersonHenrique</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>EvandroAntonio</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FabricioITAPEVA</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FERNANDAGOMEZAVA</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FernandaUmbelina</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FERNANDOGOMEZ</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FlavioHnerique</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GabrielMota</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>GIULLIANOTAVA</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>GustavoAlvesA</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>HudsonITAPEVA</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>JhonLennon</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>JoãoRolimAjU</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>JoãoVitorAVA</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>JoãoVitorR2</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>JulianoAparecido</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>KAUEBASQUEAVA</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>KhylberdAlerrandro</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>LEONARDO-ITABERA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>LucasFernando</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>LucianoITAPEVA</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MaraCorreia</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MarcosSuntak</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MarizaITAPEVA</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Mauro2</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Michele2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>MicheleCONTROLE</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MoisesOliveira</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>OdairA</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Operação01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Operação03</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Operção02</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PauloITAOCA</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PauloRoberto2</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PauloRobertoAVA</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PedroITAPEVA</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>RafaelITAPEVA</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>RaquelMonitoramento</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>RuanHenrique</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TalianeAparecida</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TamaraEmidioAVA</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TOM2</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Pendente de Cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Vanderlucio</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>VivianeSchmidtOLEO</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>WellingtonMaxwell</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>wellingtonTaquarituba</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Anjun</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Cidade Já Vinculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>iMile</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Cadastrado no Sistema</t>
         </is>
       </c>
     </row>
@@ -526,16 +6863,317 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:A44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>CIDADE CADASTRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aguas de Santa Barbara</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Apiai</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arandu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Avare</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Barao de Antonina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Barra do Chapeu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bernadino de Campos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bernardino de Campos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bom Sucesso de Itarare</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cerqueira Cesar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Coronel Macedo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fartura</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Holambra</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Iaras</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ibirarema</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Iporanga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Itabera</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Itai</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Itaoca</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Itapirapua</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Itapirapua Paulista</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Itaporanga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Itarare</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Manduri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nova Campina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Oleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ourinhos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Paranapanema</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Piraju</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ribeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ribeirao Branco</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ribeirao do Sul</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Riversul</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Salto Grande</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sao Pedro do Turvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sarutaia</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Taguai</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Taquarituba</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Taquarivai</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tejupa</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Timburi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>itararé</t>
         </is>
       </c>
     </row>
